--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65357_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65357_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R57dc50601a714c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R037449b396904d43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65357_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_65357_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R037449b396904d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0bbf7c09bb3f4c80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -5004,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5950</x:v>
+        <x:v>      0.5925</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5589,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4175</x:v>
+        <x:v>      0.4200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7869,7 +8589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0900</x:v>
+        <x:v>      1.1125</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8514,117 +9234,117 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      1.1540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      1.1700</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.3600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0575</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/02/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>11/02/2025</x:t>
         </x:is>
       </x:c>
@@ -8724,7 +9444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7400</x:v>
+        <x:v>      1.8000</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8739,7 +9459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.7933</x:v>
+        <x:v>      0.7900</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8934,7 +9654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.8567</x:v>
+        <x:v>      0.8500</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8949,13 +9669,343 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.6825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.6800</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/01/2025</x:t>
+          <x:t>13/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/01/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2024</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -8970,7 +10020,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>19/01/2025</x:t>
+          <x:t>27/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -8985,7 +10035,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/01/2025</x:t>
+          <x:t>26/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -9000,52 +10050,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>17/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/01/2025</x:t>
+          <x:t>25/12/2024</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -9060,291 +10065,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7075</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7675</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8350</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8650</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9000</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8275</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/01/2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.7425</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6200</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6700</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/12/2024</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.6800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>24/12/2024</x:t>
         </x:is>
       </x:c>
@@ -9399,7 +10119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.7833</x:v>
+        <x:v>      0.7825</x:v>
       </x:c>
     </x:row>
     <x:row>
